--- a/LISTAS_ORDENADAS/MA/Caños Cortina/CAÑOS EXTENSIBLES - CURVOS.xlsx
+++ b/LISTAS_ORDENADAS/MA/Caños Cortina/CAÑOS EXTENSIBLES - CURVOS.xlsx
@@ -752,7 +752,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="n">
-        <v>45154.58678662703</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="2">
@@ -786,7 +786,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E5" s="5" t="n"/>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D10" s="19" t="n">
-        <v>1293.6</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="11">
@@ -1010,10 +1010,8 @@
         </is>
       </c>
       <c r="C18" s="16" t="n"/>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D18" s="22" t="n">
+        <v>2509.2</v>
       </c>
     </row>
     <row r="19">
@@ -1032,10 +1030,8 @@
           <t>1 x 12</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D19" s="22" t="n">
+        <v>4218</v>
       </c>
     </row>
     <row r="20">
@@ -1054,13 +1050,10 @@
           <t>1 x 12</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="D20" s="22" t="n">
+        <v>4218</v>
+      </c>
+    </row>
     <row r="22" ht="196.5" customHeight="1" s="30"/>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -1258,19 +1251,6 @@
     <row r="33">
       <c r="D33" s="12" t="n"/>
     </row>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="29" t="n"/>
     </row>
@@ -1285,8 +1265,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.984251968503937" bottom="0.3937007874015748" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
